--- a/VerveStacks_LVA/source_data/VerveStacks_LVA.xlsx
+++ b/VerveStacks_LVA/source_data/VerveStacks_LVA.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E44172FD-AFF2-47FF-AE93-43BC6B525353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7640360-83B5-4B69-BA25-88A2C8328CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="14" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="13" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="12" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="11" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="10" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="19" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="18" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="17" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="16" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="15" r:id="rId5"/>
     <sheet name="iamc_data" sheetId="9" r:id="rId6"/>
     <sheet name="iamc_charts" sheetId="8" r:id="rId7"/>
     <sheet name="historical_data" sheetId="4" r:id="rId8"/>
@@ -1064,7 +1064,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2ACAE2-465F-723E-2548-EF266438D3E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A27811CF-B92A-58DD-CFCC-292E60DAEE05}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1119,7 +1119,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B21F3EB-1970-058B-2153-4CCE331962A0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{770DE30F-70E4-ED29-6C17-60264285AD6B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1525,7 +1525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6014C758-056E-4F7F-9DDE-890DBA88D617}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82AD20DF-A621-4480-9F1E-F34C3B5815CD}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4653,7 +4653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{241B6D99-3EC5-434E-AE90-82BFD5F832F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE646FD-82FE-435A-94A6-E045D84F174E}">
   <dimension ref="B2:L37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5848,7 +5848,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1E6253-46FC-4FA5-A570-4C6E0F7555B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944ED7BD-3B85-492E-A4D8-6F37F349DB3E}">
   <dimension ref="B2:J8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6037,7 +6037,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB218D00-8267-4AE2-ACBC-593E47E8DE79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF77272-2CEC-4FC3-98DE-B4FC01B6775D}">
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6432,7 +6432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EDBEB6-1664-49F8-960D-A23B3B7C4970}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C17A37-1A0C-4680-922B-1E10A018EBDA}">
   <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_LVA/source_data/VerveStacks_LVA.xlsx
+++ b/VerveStacks_LVA/source_data/VerveStacks_LVA.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{391C24F2-7F7C-4140-9494-0FF683CBF05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95577F18-4055-437E-A23B-E6253D4140F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="30" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="29" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="28" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="27" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="26" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="35" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="34" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="33" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="32" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="31" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="22" r:id="rId6"/>
     <sheet name="iamc_data" sheetId="9" r:id="rId7"/>
     <sheet name="iamc_charts" sheetId="8" r:id="rId8"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3097" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3165" uniqueCount="286">
   <si>
     <t>Time Slices</t>
   </si>
@@ -1044,7 +1044,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE00516F-9D31-1EE8-A941-6CF4F2569D23}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8259FF8-B61C-9EC5-4B63-90ECD2A539CB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1099,7 +1099,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E7FDAED-863E-837F-CD01-BA7C5347455D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{607E3DD1-6043-3606-1AAE-16B41D0D6357}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1505,7 +1505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004C6402-8332-4C89-A78C-91B0B099E616}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3068213-EF43-4A70-AFC2-BAE3BE5B012B}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5195,7 +5195,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B50C80-1931-4FBE-81FB-D8861C8B7372}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3445BD7A-DC06-4E56-8D55-32DEFC867CE6}">
   <dimension ref="B2:L37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6390,7 +6390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F258AB32-3F27-44C1-8D96-99187C0EE641}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491EBD98-B0B6-4374-9435-2B5D0BC8D11B}">
   <dimension ref="B2:J8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6579,7 +6579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8953F858-FDBD-471D-9868-A2F615659038}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82CB59B2-2155-41B1-BDDD-C46D1D4D318C}">
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6974,7 +6974,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD52D3E-B1A5-42CC-9F2A-31228802995C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8117650-EF9C-4913-ABCB-5CA707A778AA}">
   <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15957,6 +15957,12 @@
       <c r="C555">
         <v>2018</v>
       </c>
+      <c r="D555" t="s">
+        <v>284</v>
+      </c>
+      <c r="E555">
+        <v>1.962</v>
+      </c>
     </row>
     <row r="556" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B556" t="s">
@@ -15965,6 +15971,12 @@
       <c r="C556">
         <v>2019</v>
       </c>
+      <c r="D556" t="s">
+        <v>284</v>
+      </c>
+      <c r="E556">
+        <v>3.302</v>
+      </c>
     </row>
     <row r="557" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B557" t="s">
@@ -15973,6 +15985,12 @@
       <c r="C557">
         <v>2020</v>
       </c>
+      <c r="D557" t="s">
+        <v>284</v>
+      </c>
+      <c r="E557">
+        <v>5.1020000000000003</v>
+      </c>
     </row>
     <row r="558" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B558" t="s">
@@ -15981,6 +15999,12 @@
       <c r="C558">
         <v>2021</v>
       </c>
+      <c r="D558" t="s">
+        <v>284</v>
+      </c>
+      <c r="E558">
+        <v>7.1550000000000002</v>
+      </c>
     </row>
     <row r="559" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B559" t="s">
@@ -15989,6 +16013,12 @@
       <c r="C559">
         <v>2022</v>
       </c>
+      <c r="D559" t="s">
+        <v>284</v>
+      </c>
+      <c r="E559">
+        <v>113</v>
+      </c>
     </row>
     <row r="560" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B560" t="s">
@@ -15997,389 +16027,683 @@
       <c r="C560">
         <v>2023</v>
       </c>
-    </row>
-    <row r="561" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D560" t="s">
+        <v>284</v>
+      </c>
+      <c r="E560">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="561" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B561" t="s">
         <v>87</v>
       </c>
       <c r="C561">
         <v>2024</v>
       </c>
-    </row>
-    <row r="562" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D561" t="s">
+        <v>284</v>
+      </c>
+      <c r="E561">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="562" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B562" t="s">
         <v>87</v>
       </c>
       <c r="C562">
         <v>2016</v>
       </c>
-    </row>
-    <row r="563" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D562" t="s">
+        <v>284</v>
+      </c>
+      <c r="E562">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="563" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B563" t="s">
         <v>87</v>
       </c>
       <c r="C563">
         <v>2017</v>
       </c>
-    </row>
-    <row r="564" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D563" t="s">
+        <v>284</v>
+      </c>
+      <c r="E563">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="564" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B564" t="s">
         <v>87</v>
       </c>
       <c r="C564">
         <v>2012</v>
       </c>
-    </row>
-    <row r="565" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D564" t="s">
+        <v>283</v>
+      </c>
+      <c r="E564">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="565" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B565" t="s">
         <v>87</v>
       </c>
       <c r="C565">
         <v>2013</v>
       </c>
-    </row>
-    <row r="566" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D565" t="s">
+        <v>283</v>
+      </c>
+      <c r="E565">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="566" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B566" t="s">
         <v>87</v>
       </c>
       <c r="C566">
         <v>2014</v>
       </c>
-    </row>
-    <row r="567" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D566" t="s">
+        <v>283</v>
+      </c>
+      <c r="E566">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="567" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B567" t="s">
         <v>87</v>
       </c>
       <c r="C567">
         <v>2015</v>
       </c>
-    </row>
-    <row r="568" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D567" t="s">
+        <v>283</v>
+      </c>
+      <c r="E567">
+        <v>0.23499999999999999</v>
+      </c>
+    </row>
+    <row r="568" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B568" t="s">
         <v>87</v>
       </c>
       <c r="C568">
         <v>2016</v>
       </c>
-    </row>
-    <row r="569" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D568" t="s">
+        <v>283</v>
+      </c>
+      <c r="E568">
+        <v>0.38200000000000001</v>
+      </c>
+    </row>
+    <row r="569" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B569" t="s">
         <v>87</v>
       </c>
       <c r="C569">
         <v>2017</v>
       </c>
-    </row>
-    <row r="570" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D569" t="s">
+        <v>283</v>
+      </c>
+      <c r="E569">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="570" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B570" t="s">
         <v>87</v>
       </c>
       <c r="C570">
         <v>2018</v>
       </c>
-    </row>
-    <row r="571" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D570" t="s">
+        <v>283</v>
+      </c>
+      <c r="E570">
+        <v>1.2729999999999999</v>
+      </c>
+    </row>
+    <row r="571" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B571" t="s">
         <v>87</v>
       </c>
       <c r="C571">
         <v>2019</v>
       </c>
-    </row>
-    <row r="572" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D571" t="s">
+        <v>283</v>
+      </c>
+      <c r="E571">
+        <v>3.137</v>
+      </c>
+    </row>
+    <row r="572" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B572" t="s">
         <v>87</v>
       </c>
       <c r="C572">
         <v>2020</v>
       </c>
-    </row>
-    <row r="573" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D572" t="s">
+        <v>283</v>
+      </c>
+      <c r="E572">
+        <v>4.8470000000000004</v>
+      </c>
+    </row>
+    <row r="573" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B573" t="s">
         <v>87</v>
       </c>
       <c r="C573">
         <v>2021</v>
       </c>
-    </row>
-    <row r="574" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D573" t="s">
+        <v>283</v>
+      </c>
+      <c r="E573">
+        <v>6.7969999999999997</v>
+      </c>
+    </row>
+    <row r="574" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B574" t="s">
         <v>87</v>
       </c>
       <c r="C574">
         <v>2022</v>
       </c>
-    </row>
-    <row r="575" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D574" t="s">
+        <v>283</v>
+      </c>
+      <c r="E574">
+        <v>41.276000000000003</v>
+      </c>
+    </row>
+    <row r="575" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B575" t="s">
         <v>238</v>
       </c>
       <c r="C575">
         <v>2018</v>
       </c>
-    </row>
-    <row r="576" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D575" t="s">
+        <v>284</v>
+      </c>
+      <c r="E575">
+        <v>78.171999999999997</v>
+      </c>
+    </row>
+    <row r="576" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B576" t="s">
         <v>238</v>
       </c>
       <c r="C576">
         <v>2019</v>
       </c>
-    </row>
-    <row r="577" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D576" t="s">
+        <v>284</v>
+      </c>
+      <c r="E576">
+        <v>78.171999999999997</v>
+      </c>
+    </row>
+    <row r="577" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B577" t="s">
         <v>238</v>
       </c>
       <c r="C577">
         <v>2020</v>
       </c>
-    </row>
-    <row r="578" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D577" t="s">
+        <v>284</v>
+      </c>
+      <c r="E577">
+        <v>78.171999999999997</v>
+      </c>
+    </row>
+    <row r="578" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B578" t="s">
         <v>238</v>
       </c>
       <c r="C578">
         <v>2021</v>
       </c>
-    </row>
-    <row r="579" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D578" t="s">
+        <v>284</v>
+      </c>
+      <c r="E578">
+        <v>77.129000000000005</v>
+      </c>
+    </row>
+    <row r="579" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B579" t="s">
         <v>238</v>
       </c>
       <c r="C579">
         <v>2022</v>
       </c>
-    </row>
-    <row r="580" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D579" t="s">
+        <v>284</v>
+      </c>
+      <c r="E579">
+        <v>82.426000000000002</v>
+      </c>
+    </row>
+    <row r="580" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B580" t="s">
         <v>238</v>
       </c>
       <c r="C580">
         <v>2023</v>
       </c>
-    </row>
-    <row r="581" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D580" t="s">
+        <v>284</v>
+      </c>
+      <c r="E580">
+        <v>128.268</v>
+      </c>
+    </row>
+    <row r="581" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B581" t="s">
         <v>238</v>
       </c>
       <c r="C581">
         <v>2024</v>
       </c>
-    </row>
-    <row r="582" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D581" t="s">
+        <v>284</v>
+      </c>
+      <c r="E581">
+        <v>128.268</v>
+      </c>
+    </row>
+    <row r="582" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B582" t="s">
         <v>238</v>
       </c>
       <c r="C582">
         <v>2011</v>
       </c>
-    </row>
-    <row r="583" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D582" t="s">
+        <v>284</v>
+      </c>
+      <c r="E582">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="583" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B583" t="s">
         <v>238</v>
       </c>
       <c r="C583">
         <v>2012</v>
       </c>
-    </row>
-    <row r="584" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D583" t="s">
+        <v>284</v>
+      </c>
+      <c r="E583">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="584" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B584" t="s">
         <v>238</v>
       </c>
       <c r="C584">
         <v>2013</v>
       </c>
-    </row>
-    <row r="585" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D584" t="s">
+        <v>284</v>
+      </c>
+      <c r="E584">
+        <v>65.891999999999996</v>
+      </c>
+    </row>
+    <row r="585" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B585" t="s">
         <v>238</v>
       </c>
       <c r="C585">
         <v>2014</v>
       </c>
-    </row>
-    <row r="586" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D585" t="s">
+        <v>284</v>
+      </c>
+      <c r="E585">
+        <v>68.915000000000006</v>
+      </c>
+    </row>
+    <row r="586" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B586" t="s">
         <v>238</v>
       </c>
       <c r="C586">
         <v>2015</v>
       </c>
-    </row>
-    <row r="587" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D586" t="s">
+        <v>284</v>
+      </c>
+      <c r="E586">
+        <v>68.165000000000006</v>
+      </c>
+    </row>
+    <row r="587" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B587" t="s">
         <v>238</v>
       </c>
       <c r="C587">
         <v>2016</v>
       </c>
-    </row>
-    <row r="588" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D587" t="s">
+        <v>284</v>
+      </c>
+      <c r="E587">
+        <v>69.905000000000001</v>
+      </c>
+    </row>
+    <row r="588" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B588" t="s">
         <v>238</v>
       </c>
       <c r="C588">
         <v>2017</v>
       </c>
-    </row>
-    <row r="589" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D588" t="s">
+        <v>284</v>
+      </c>
+      <c r="E588">
+        <v>77.105000000000004</v>
+      </c>
+    </row>
+    <row r="589" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B589" t="s">
         <v>238</v>
       </c>
       <c r="C589">
         <v>2004</v>
       </c>
-    </row>
-    <row r="590" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D589" t="s">
+        <v>284</v>
+      </c>
+      <c r="E589">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="590" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B590" t="s">
         <v>238</v>
       </c>
       <c r="C590">
         <v>2005</v>
       </c>
-    </row>
-    <row r="591" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D590" t="s">
+        <v>284</v>
+      </c>
+      <c r="E590">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="591" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B591" t="s">
         <v>238</v>
       </c>
       <c r="C591">
         <v>2006</v>
       </c>
-    </row>
-    <row r="592" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D591" t="s">
+        <v>284</v>
+      </c>
+      <c r="E591">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="592" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B592" t="s">
         <v>238</v>
       </c>
       <c r="C592">
         <v>2007</v>
       </c>
-    </row>
-    <row r="593" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D592" t="s">
+        <v>284</v>
+      </c>
+      <c r="E592">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="593" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B593" t="s">
         <v>238</v>
       </c>
       <c r="C593">
         <v>2008</v>
       </c>
-    </row>
-    <row r="594" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D593" t="s">
+        <v>284</v>
+      </c>
+      <c r="E593">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="594" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B594" t="s">
         <v>238</v>
       </c>
       <c r="C594">
         <v>2009</v>
       </c>
-    </row>
-    <row r="595" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D594" t="s">
+        <v>284</v>
+      </c>
+      <c r="E594">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="595" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B595" t="s">
         <v>238</v>
       </c>
       <c r="C595">
         <v>2010</v>
       </c>
-    </row>
-    <row r="596" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D595" t="s">
+        <v>284</v>
+      </c>
+      <c r="E595">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="596" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B596" t="s">
         <v>238</v>
       </c>
       <c r="C596">
         <v>2000</v>
       </c>
-    </row>
-    <row r="597" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D596" t="s">
+        <v>284</v>
+      </c>
+      <c r="E596">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="597" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B597" t="s">
         <v>238</v>
       </c>
       <c r="C597">
         <v>2001</v>
       </c>
-    </row>
-    <row r="598" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D597" t="s">
+        <v>284</v>
+      </c>
+      <c r="E597">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="598" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B598" t="s">
         <v>238</v>
       </c>
       <c r="C598">
         <v>2002</v>
       </c>
-    </row>
-    <row r="599" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D598" t="s">
+        <v>284</v>
+      </c>
+      <c r="E598">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="599" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B599" t="s">
         <v>238</v>
       </c>
       <c r="C599">
         <v>2003</v>
       </c>
-    </row>
-    <row r="600" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D599" t="s">
+        <v>284</v>
+      </c>
+      <c r="E599">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="600" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B600" t="s">
         <v>238</v>
       </c>
       <c r="C600">
         <v>2002</v>
       </c>
-    </row>
-    <row r="601" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D600" t="s">
+        <v>283</v>
+      </c>
+      <c r="E600">
+        <v>11.242000000000001</v>
+      </c>
+    </row>
+    <row r="601" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B601" t="s">
         <v>238</v>
       </c>
       <c r="C601">
         <v>2003</v>
       </c>
-    </row>
-    <row r="602" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D601" t="s">
+        <v>283</v>
+      </c>
+      <c r="E601">
+        <v>48.445999999999998</v>
+      </c>
+    </row>
+    <row r="602" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B602" t="s">
         <v>238</v>
       </c>
       <c r="C602">
         <v>2004</v>
       </c>
-    </row>
-    <row r="603" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D602" t="s">
+        <v>283</v>
+      </c>
+      <c r="E602">
+        <v>49.146999999999998</v>
+      </c>
+    </row>
+    <row r="603" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B603" t="s">
         <v>238</v>
       </c>
       <c r="C603">
         <v>2005</v>
       </c>
-    </row>
-    <row r="604" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D603" t="s">
+        <v>283</v>
+      </c>
+      <c r="E603">
+        <v>46.853999999999999</v>
+      </c>
+    </row>
+    <row r="604" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B604" t="s">
         <v>238</v>
       </c>
       <c r="C604">
         <v>2006</v>
       </c>
-    </row>
-    <row r="605" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D604" t="s">
+        <v>283</v>
+      </c>
+      <c r="E604">
+        <v>46.212000000000003</v>
+      </c>
+    </row>
+    <row r="605" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B605" t="s">
         <v>238</v>
       </c>
       <c r="C605">
         <v>2007</v>
       </c>
-    </row>
-    <row r="606" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D605" t="s">
+        <v>283</v>
+      </c>
+      <c r="E605">
+        <v>52.929000000000002</v>
+      </c>
+    </row>
+    <row r="606" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B606" t="s">
         <v>238</v>
       </c>
       <c r="C606">
         <v>2008</v>
       </c>
-    </row>
-    <row r="607" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D606" t="s">
+        <v>283</v>
+      </c>
+      <c r="E606">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="607" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B607" t="s">
         <v>238</v>
       </c>
       <c r="C607">
         <v>2009</v>
       </c>
-    </row>
-    <row r="608" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D607" t="s">
+        <v>283</v>
+      </c>
+      <c r="E607">
+        <v>50.088999999999999</v>
+      </c>
+    </row>
+    <row r="608" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B608" t="s">
         <v>238</v>
       </c>
       <c r="C608">
         <v>2010</v>
+      </c>
+      <c r="D608" t="s">
+        <v>283</v>
+      </c>
+      <c r="E608">
+        <v>49.057000000000002</v>
       </c>
     </row>
     <row r="609" spans="2:5" x14ac:dyDescent="0.45">
@@ -16389,6 +16713,12 @@
       <c r="C609">
         <v>2011</v>
       </c>
+      <c r="D609" t="s">
+        <v>283</v>
+      </c>
+      <c r="E609">
+        <v>70.894000000000005</v>
+      </c>
     </row>
     <row r="610" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B610" t="s">
@@ -16397,6 +16727,12 @@
       <c r="C610">
         <v>2012</v>
       </c>
+      <c r="D610" t="s">
+        <v>283</v>
+      </c>
+      <c r="E610">
+        <v>114.26600000000001</v>
+      </c>
     </row>
     <row r="611" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B611" t="s">
@@ -16405,6 +16741,12 @@
       <c r="C611">
         <v>2013</v>
       </c>
+      <c r="D611" t="s">
+        <v>283</v>
+      </c>
+      <c r="E611">
+        <v>120.05500000000001</v>
+      </c>
     </row>
     <row r="612" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B612" t="s">
@@ -16413,6 +16755,12 @@
       <c r="C612">
         <v>2014</v>
       </c>
+      <c r="D612" t="s">
+        <v>283</v>
+      </c>
+      <c r="E612">
+        <v>139.71199999999999</v>
+      </c>
     </row>
     <row r="613" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B613" t="s">
@@ -16421,6 +16769,12 @@
       <c r="C613">
         <v>2015</v>
       </c>
+      <c r="D613" t="s">
+        <v>283</v>
+      </c>
+      <c r="E613">
+        <v>147.13499999999999</v>
+      </c>
     </row>
     <row r="614" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B614" t="s">
@@ -16429,6 +16783,12 @@
       <c r="C614">
         <v>2016</v>
       </c>
+      <c r="D614" t="s">
+        <v>283</v>
+      </c>
+      <c r="E614">
+        <v>127.889</v>
+      </c>
     </row>
     <row r="615" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B615" t="s">
@@ -16437,6 +16797,12 @@
       <c r="C615">
         <v>2017</v>
       </c>
+      <c r="D615" t="s">
+        <v>283</v>
+      </c>
+      <c r="E615">
+        <v>150</v>
+      </c>
     </row>
     <row r="616" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B616" t="s">
@@ -16445,6 +16811,12 @@
       <c r="C616">
         <v>2018</v>
       </c>
+      <c r="D616" t="s">
+        <v>283</v>
+      </c>
+      <c r="E616">
+        <v>122.038</v>
+      </c>
     </row>
     <row r="617" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B617" t="s">
@@ -16453,6 +16825,12 @@
       <c r="C617">
         <v>2019</v>
       </c>
+      <c r="D617" t="s">
+        <v>283</v>
+      </c>
+      <c r="E617">
+        <v>153.999</v>
+      </c>
     </row>
     <row r="618" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B618" t="s">
@@ -16461,6 +16839,12 @@
       <c r="C618">
         <v>2020</v>
       </c>
+      <c r="D618" t="s">
+        <v>283</v>
+      </c>
+      <c r="E618">
+        <v>176.84200000000001</v>
+      </c>
     </row>
     <row r="619" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B619" t="s">
@@ -16469,6 +16853,12 @@
       <c r="C619">
         <v>2021</v>
       </c>
+      <c r="D619" t="s">
+        <v>283</v>
+      </c>
+      <c r="E619">
+        <v>141.43600000000001</v>
+      </c>
     </row>
     <row r="620" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B620" t="s">
@@ -16477,6 +16867,12 @@
       <c r="C620">
         <v>2022</v>
       </c>
+      <c r="D620" t="s">
+        <v>283</v>
+      </c>
+      <c r="E620">
+        <v>190.18299999999999</v>
+      </c>
     </row>
     <row r="621" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B621" t="s">
@@ -16485,6 +16881,12 @@
       <c r="C621">
         <v>2000</v>
       </c>
+      <c r="D621" t="s">
+        <v>283</v>
+      </c>
+      <c r="E621">
+        <v>4.4169999999999998</v>
+      </c>
     </row>
     <row r="622" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B622" t="s">
@@ -16492,6 +16894,12 @@
       </c>
       <c r="C622">
         <v>2001</v>
+      </c>
+      <c r="D622" t="s">
+        <v>283</v>
+      </c>
+      <c r="E622">
+        <v>3.4329999999999998</v>
       </c>
     </row>
     <row r="623" spans="2:5" x14ac:dyDescent="0.45">

--- a/VerveStacks_LVA/source_data/VerveStacks_LVA.xlsx
+++ b/VerveStacks_LVA/source_data/VerveStacks_LVA.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95577F18-4055-437E-A23B-E6253D4140F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3B99FF9-A579-4800-B120-7A0F21BBB60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="35" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="34" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="33" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="32" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="31" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="40" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="39" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="38" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="37" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="36" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="22" r:id="rId6"/>
     <sheet name="iamc_data" sheetId="9" r:id="rId7"/>
     <sheet name="iamc_charts" sheetId="8" r:id="rId8"/>
@@ -1044,7 +1044,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8259FF8-B61C-9EC5-4B63-90ECD2A539CB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6873573A-B551-22EB-BB1B-F48233608CC5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1099,7 +1099,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{607E3DD1-6043-3606-1AAE-16B41D0D6357}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D23DAFE5-D5EB-AA20-F6BF-81DB8AE6C5A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1505,7 +1505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3068213-EF43-4A70-AFC2-BAE3BE5B012B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC68108-0437-42FF-83F2-4527354260B0}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5195,7 +5195,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3445BD7A-DC06-4E56-8D55-32DEFC867CE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A155319E-1D57-49FB-8B6B-AC5B754D5E8B}">
   <dimension ref="B2:L37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6390,7 +6390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491EBD98-B0B6-4374-9435-2B5D0BC8D11B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCF33FA-46C7-4381-BB4D-A39FB8660221}">
   <dimension ref="B2:J8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6579,7 +6579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82CB59B2-2155-41B1-BDDD-C46D1D4D318C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B181C6-013E-4191-9411-00D0E7DCE5FB}">
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6974,7 +6974,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8117650-EF9C-4913-ABCB-5CA707A778AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B81F47B-9D1E-4C75-83A5-5A965996B255}">
   <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
